--- a/data/PricesNP.xlsx
+++ b/data/PricesNP.xlsx
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>81.7</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="2">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.39</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="3">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.48999999999999</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.22</v>
+        <v>115.25</v>
       </c>
     </row>
     <row r="5">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.69</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.78</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.53</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.20999999999999</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="9">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.97</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="10">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.34</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="11">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82.51000000000001</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82.84</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="13">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.83</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="14">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.5</v>
+        <v>111.79</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78.98</v>
+        <v>111.45</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>78.73999999999999</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75.86</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="18">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>76.28</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="19">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76.19</v>
+        <v>111.85</v>
       </c>
     </row>
     <row r="20">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>76.17</v>
+        <v>112.57</v>
       </c>
     </row>
     <row r="21">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.75</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="22">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>73.88</v>
+        <v>113.58</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>74.18000000000001</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="24">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73.86</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>71.84</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="26">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>71.95999999999999</v>
+        <v>112.99</v>
       </c>
     </row>
     <row r="27">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74.06</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="28">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>73.84</v>
+        <v>112.97</v>
       </c>
     </row>
     <row r="29">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>73.83</v>
+        <v>117.54</v>
       </c>
     </row>
     <row r="30">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>74.05</v>
+        <v>115.39</v>
       </c>
     </row>
     <row r="31">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>72.52</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="32">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>72.84</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="33">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>74.98</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="34">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>74.73999999999999</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="35">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>70.90000000000001</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="36">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>62.12</v>
+        <v>106.15</v>
       </c>
     </row>
     <row r="37">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>74.45</v>
+        <v>107.49</v>
       </c>
     </row>
     <row r="38">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82.28</v>
+        <v>106.04</v>
       </c>
     </row>
     <row r="39">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>84.37</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="40">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>84.39</v>
+        <v>103.92</v>
       </c>
     </row>
     <row r="41">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81.78</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="42">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81.94</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="43">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>82.63</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="44">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>82.92</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="45">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>75.33</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="46">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>75.06999999999999</v>
+        <v>98.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>74.90000000000001</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="48">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>74.97</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="49">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>79.11</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="50">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>79.08</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>79.06</v>
+        <v>96.36</v>
       </c>
     </row>
     <row r="52">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>79.04000000000001</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>77.91</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>77.3</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="55">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>76.93000000000001</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="56">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>76.52</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>77.3</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="58">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>76.77</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>74.68000000000001</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>76.79000000000001</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="61">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>77.92</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>75.67</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>74.27</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="64">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>77.55</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>75</v>
+        <v>105.68</v>
       </c>
     </row>
     <row r="66">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>82.92</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="67">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>87.34999999999999</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="68">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>90.48</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="69">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>90.73999999999999</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="70">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>92.79000000000001</v>
+        <v>112.63</v>
       </c>
     </row>
     <row r="71">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>93.45</v>
+        <v>120.81</v>
       </c>
     </row>
     <row r="72">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>94.04000000000001</v>
+        <v>123.97</v>
       </c>
     </row>
     <row r="73">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>94.47</v>
+        <v>126.52</v>
       </c>
     </row>
     <row r="74">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>94.73</v>
+        <v>129.06</v>
       </c>
     </row>
     <row r="75">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>95.2</v>
+        <v>134.77</v>
       </c>
     </row>
     <row r="76">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>95.28</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="77">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>95.87</v>
+        <v>149.58</v>
       </c>
     </row>
     <row r="78">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>95.19</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="79">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>94.45999999999999</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="80">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>94.40000000000001</v>
+        <v>128.93</v>
       </c>
     </row>
     <row r="81">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>93.79000000000001</v>
+        <v>127.45</v>
       </c>
     </row>
     <row r="82">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>92.64</v>
+        <v>126.91</v>
       </c>
     </row>
     <row r="83">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>91.56999999999999</v>
+        <v>123.56</v>
       </c>
     </row>
     <row r="84">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>89.18000000000001</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="85">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>89.25</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="86">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>87.03</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="87">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>84</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="88">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>81.09999999999999</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="89">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>84.04000000000001</v>
+        <v>119.67</v>
       </c>
     </row>
     <row r="90">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>82.05</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="91">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>77.92</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="92">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>75.88</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="93">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>77.31</v>
+        <v>114.65</v>
       </c>
     </row>
     <row r="94">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>75.33</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="95">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>75.08</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="96">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>74.56999999999999</v>
+        <v>112.03</v>
       </c>
     </row>
     <row r="97">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>81.7</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="98">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>80.39</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="99">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>80.48999999999999</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="100">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>79.22</v>
+        <v>115.25</v>
       </c>
     </row>
     <row r="101">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>82.69</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="102">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>82.78</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="103">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>82.53</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="104">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>81.20999999999999</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="105">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>81.97</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="106">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>82.34</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="107">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>82.51000000000001</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="108">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>82.84</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="109">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>77.83</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="110">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>78.5</v>
+        <v>111.79</v>
       </c>
     </row>
     <row r="111">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>78.98</v>
+        <v>111.45</v>
       </c>
     </row>
     <row r="112">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>78.73999999999999</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="113">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>75.86</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="114">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>76.28</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="115">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>76.19</v>
+        <v>111.85</v>
       </c>
     </row>
     <row r="116">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>76.17</v>
+        <v>112.57</v>
       </c>
     </row>
     <row r="117">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>72.75</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="118">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>73.88</v>
+        <v>113.58</v>
       </c>
     </row>
     <row r="119">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>74.18000000000001</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="120">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>73.86</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="121">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>71.84</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="122">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>71.95999999999999</v>
+        <v>112.99</v>
       </c>
     </row>
     <row r="123">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>74.06</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="124">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>73.84</v>
+        <v>112.97</v>
       </c>
     </row>
     <row r="125">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>73.83</v>
+        <v>117.54</v>
       </c>
     </row>
     <row r="126">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>74.05</v>
+        <v>115.39</v>
       </c>
     </row>
     <row r="127">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>72.52</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="128">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>72.84</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="129">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>74.98</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="130">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>74.73999999999999</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="131">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>70.90000000000001</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="132">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>62.12</v>
+        <v>106.15</v>
       </c>
     </row>
     <row r="133">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>74.45</v>
+        <v>107.49</v>
       </c>
     </row>
     <row r="134">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>82.28</v>
+        <v>106.04</v>
       </c>
     </row>
     <row r="135">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>84.37</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="136">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>84.39</v>
+        <v>103.92</v>
       </c>
     </row>
     <row r="137">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>81.78</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="138">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>81.94</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="139">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>82.63</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="140">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>82.92</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="141">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>75.33</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="142">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>75.06999999999999</v>
+        <v>98.79000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>74.90000000000001</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="144">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>74.97</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="145">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>79.11</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="146">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>79.08</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>79.06</v>
+        <v>96.36</v>
       </c>
     </row>
     <row r="148">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>79.04000000000001</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>77.91</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>77.3</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="151">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>76.93000000000001</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="152">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>76.52</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>77.3</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="154">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>76.77</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>74.68000000000001</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="156">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>76.79000000000001</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="157">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>77.92</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="158">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>75.67</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="159">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>74.27</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="160">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>77.55</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="161">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>75</v>
+        <v>105.68</v>
       </c>
     </row>
     <row r="162">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>82.92</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="163">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>87.34999999999999</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="164">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>90.48</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="165">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>90.73999999999999</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="166">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>92.79000000000001</v>
+        <v>112.63</v>
       </c>
     </row>
     <row r="167">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>93.45</v>
+        <v>120.81</v>
       </c>
     </row>
     <row r="168">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>94.04000000000001</v>
+        <v>123.97</v>
       </c>
     </row>
     <row r="169">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>94.47</v>
+        <v>126.52</v>
       </c>
     </row>
     <row r="170">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>94.73</v>
+        <v>129.06</v>
       </c>
     </row>
     <row r="171">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>95.2</v>
+        <v>134.77</v>
       </c>
     </row>
     <row r="172">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>95.28</v>
+        <v>135.68</v>
       </c>
     </row>
     <row r="173">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>95.87</v>
+        <v>149.58</v>
       </c>
     </row>
     <row r="174">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>95.19</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="175">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>94.45999999999999</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="176">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>94.40000000000001</v>
+        <v>128.93</v>
       </c>
     </row>
     <row r="177">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>93.79000000000001</v>
+        <v>127.45</v>
       </c>
     </row>
     <row r="178">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>92.64</v>
+        <v>126.91</v>
       </c>
     </row>
     <row r="179">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>91.56999999999999</v>
+        <v>123.56</v>
       </c>
     </row>
     <row r="180">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>89.18000000000001</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="181">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>89.25</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="182">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>87.03</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="183">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>84</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="184">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>81.09999999999999</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="185">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>84.04000000000001</v>
+        <v>119.67</v>
       </c>
     </row>
     <row r="186">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>82.05</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="187">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>77.92</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="188">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>75.88</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="189">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>77.31</v>
+        <v>114.65</v>
       </c>
     </row>
     <row r="190">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>75.33</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="191">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>75.08</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="192">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>74.56999999999999</v>
+        <v>112.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/PricesNP.xlsx
+++ b/data/PricesNP.xlsx
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>112.88</v>
+        <v>108.29</v>
       </c>
     </row>
     <row r="2">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>113.68</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="3">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113.36</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.79</v>
+        <v>106.16</v>
       </c>
     </row>
     <row r="5">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.2</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.99</v>
+        <v>105.79</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.73</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.66</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="9">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113.99</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="10">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113.63</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="11">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>113.31</v>
+        <v>105.85</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>112.99</v>
+        <v>105.84</v>
       </c>
     </row>
     <row r="13">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>112.21</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="14">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>112.29</v>
+        <v>106.32</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112.16</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>112.22</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112.05</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="18">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>111.92</v>
+        <v>108.91</v>
       </c>
     </row>
     <row r="19">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>111.8</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="20">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111.77</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="21">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>112.34</v>
+        <v>109.88</v>
       </c>
     </row>
     <row r="22">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>112.13</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>111.95</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="24">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>111.88</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116.77</v>
+        <v>115.41</v>
       </c>
     </row>
     <row r="26">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>117.47</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="27">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>117.75</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="28">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>117.73</v>
+        <v>124.79</v>
       </c>
     </row>
     <row r="29">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>113.96</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="30">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>110.44</v>
+        <v>143.73</v>
       </c>
     </row>
     <row r="31">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>108.23</v>
+        <v>145.14</v>
       </c>
     </row>
     <row r="32">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>106.96</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="33">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>109.55</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="34">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107.83</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="35">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>106.19</v>
+        <v>136.83</v>
       </c>
     </row>
     <row r="36">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>105.28</v>
+        <v>117.41</v>
       </c>
     </row>
     <row r="37">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>105.49</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="38">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>104.76</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="39">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>102.82</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="40">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>100.53</v>
+        <v>110.02</v>
       </c>
     </row>
     <row r="41">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>101.84</v>
+        <v>110.38</v>
       </c>
     </row>
     <row r="42">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>99.88</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="43">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>96.95999999999999</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="44">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>95.48</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="45">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>96.16</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="46">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>96.44</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="47">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>96.43000000000001</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="48">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>96.45</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="49">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>96.52</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>96.52</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="51">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>96.51000000000001</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="52">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>96.39</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>96.59</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>96.63</v>
+        <v>98.29000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>96.67</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="56">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>96.56999999999999</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>96.28</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="58">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>96.23999999999999</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="59">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>96.23999999999999</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="60">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>97.5</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="61">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>98.94</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100.47</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="63">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>103.21</v>
+        <v>110.29</v>
       </c>
     </row>
     <row r="64">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>104.99</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>103.51</v>
+        <v>110.83</v>
       </c>
     </row>
     <row r="66">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>105.9</v>
+        <v>115.82</v>
       </c>
     </row>
     <row r="67">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>107.61</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="68">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>108.3</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="69">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>109.76</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="70">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>115.95</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="71">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>120.98</v>
+        <v>172.14</v>
       </c>
     </row>
     <row r="72">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>124.86</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="73">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>126.55</v>
+        <v>186.72</v>
       </c>
     </row>
     <row r="74">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>135.49</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="75">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>131.81</v>
+        <v>191.2</v>
       </c>
     </row>
     <row r="76">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>130.45</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="77">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>130.38</v>
+        <v>165.74</v>
       </c>
     </row>
     <row r="78">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>128.79</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="79">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>126.16</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="80">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>124.94</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="81">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>124.48</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="82">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>123.55</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="83">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>121.56</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="84">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>119.7</v>
+        <v>138.64</v>
       </c>
     </row>
     <row r="85">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>121.13</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="86">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>119.95</v>
+        <v>148.84</v>
       </c>
     </row>
     <row r="87">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>118.05</v>
+        <v>135.12</v>
       </c>
     </row>
     <row r="88">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>111.27</v>
+        <v>127.76</v>
       </c>
     </row>
     <row r="89">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>117.92</v>
+        <v>129.46</v>
       </c>
     </row>
     <row r="90">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>114.25</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="91">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>111.74</v>
+        <v>124.28</v>
       </c>
     </row>
     <row r="92">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>110.51</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="93">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>110.8</v>
+        <v>118.26</v>
       </c>
     </row>
     <row r="94">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>108.55</v>
+        <v>117.66</v>
       </c>
     </row>
     <row r="95">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>107.4</v>
+        <v>117.49</v>
       </c>
     </row>
     <row r="96">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>106.19</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="97">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>112.88</v>
+        <v>108.29</v>
       </c>
     </row>
     <row r="98">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>113.68</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="99">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>113.36</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="100">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>112.79</v>
+        <v>106.16</v>
       </c>
     </row>
     <row r="101">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>112.2</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="102">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>112.99</v>
+        <v>105.79</v>
       </c>
     </row>
     <row r="103">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>112.73</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="104">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>112.66</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="105">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>113.99</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="106">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>113.63</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="107">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>113.31</v>
+        <v>105.85</v>
       </c>
     </row>
     <row r="108">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>112.99</v>
+        <v>105.84</v>
       </c>
     </row>
     <row r="109">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>112.21</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="110">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>112.29</v>
+        <v>106.32</v>
       </c>
     </row>
     <row r="111">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>112.16</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="112">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>112.22</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="113">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>112.05</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="114">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>111.92</v>
+        <v>108.91</v>
       </c>
     </row>
     <row r="115">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>111.8</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="116">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>111.77</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="117">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>112.34</v>
+        <v>109.88</v>
       </c>
     </row>
     <row r="118">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>112.13</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="119">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>111.95</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="120">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>111.88</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="121">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>116.77</v>
+        <v>115.41</v>
       </c>
     </row>
     <row r="122">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>117.47</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="123">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>117.75</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="124">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>117.73</v>
+        <v>124.79</v>
       </c>
     </row>
     <row r="125">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>113.96</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="126">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>110.44</v>
+        <v>143.73</v>
       </c>
     </row>
     <row r="127">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>108.23</v>
+        <v>145.14</v>
       </c>
     </row>
     <row r="128">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>106.96</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="129">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>109.55</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="130">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>107.83</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="131">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>106.19</v>
+        <v>136.83</v>
       </c>
     </row>
     <row r="132">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>105.28</v>
+        <v>117.41</v>
       </c>
     </row>
     <row r="133">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>105.49</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="134">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>104.76</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="135">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>102.82</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="136">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>100.53</v>
+        <v>110.02</v>
       </c>
     </row>
     <row r="137">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>101.84</v>
+        <v>110.38</v>
       </c>
     </row>
     <row r="138">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>99.88</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="139">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>96.95999999999999</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="140">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>95.48</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="141">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>96.16</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="142">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>96.44</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="143">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>96.43000000000001</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="144">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>96.45</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="145">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>96.52</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>96.52</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="147">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>96.51000000000001</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="148">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>96.39</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>96.59</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>96.63</v>
+        <v>98.29000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>96.67</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="152">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>96.56999999999999</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>96.28</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="154">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>96.23999999999999</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="155">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>96.23999999999999</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="156">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>97.5</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="157">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>98.94</v>
+        <v>105.95</v>
       </c>
     </row>
     <row r="158">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>100.47</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="159">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>103.21</v>
+        <v>110.29</v>
       </c>
     </row>
     <row r="160">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>104.99</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="161">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>103.51</v>
+        <v>110.83</v>
       </c>
     </row>
     <row r="162">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>105.9</v>
+        <v>115.82</v>
       </c>
     </row>
     <row r="163">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>107.61</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="164">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>108.3</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="165">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>109.76</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="166">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>115.95</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="167">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>120.98</v>
+        <v>172.14</v>
       </c>
     </row>
     <row r="168">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>124.86</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="169">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>126.55</v>
+        <v>186.72</v>
       </c>
     </row>
     <row r="170">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>135.49</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="171">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>131.81</v>
+        <v>191.2</v>
       </c>
     </row>
     <row r="172">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>130.45</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="173">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>130.38</v>
+        <v>165.74</v>
       </c>
     </row>
     <row r="174">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>128.79</v>
+        <v>137.23</v>
       </c>
     </row>
     <row r="175">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>126.16</v>
+        <v>140.31</v>
       </c>
     </row>
     <row r="176">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>124.94</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="177">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>124.48</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="178">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>123.55</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="179">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>121.56</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="180">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>119.7</v>
+        <v>138.64</v>
       </c>
     </row>
     <row r="181">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>121.13</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="182">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>119.95</v>
+        <v>148.84</v>
       </c>
     </row>
     <row r="183">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>118.05</v>
+        <v>135.12</v>
       </c>
     </row>
     <row r="184">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>111.27</v>
+        <v>127.76</v>
       </c>
     </row>
     <row r="185">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>117.92</v>
+        <v>129.46</v>
       </c>
     </row>
     <row r="186">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>114.25</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="187">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>111.74</v>
+        <v>124.28</v>
       </c>
     </row>
     <row r="188">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>110.51</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="189">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>110.8</v>
+        <v>118.26</v>
       </c>
     </row>
     <row r="190">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>108.55</v>
+        <v>117.66</v>
       </c>
     </row>
     <row r="191">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>107.4</v>
+        <v>117.49</v>
       </c>
     </row>
     <row r="192">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>106.19</v>
+        <v>117.23</v>
       </c>
     </row>
   </sheetData>
